--- a/30_Threshold_OUTPUT/direct_P61609_Geobacter_sulfurreducens_PCA.xlsx
+++ b/30_Threshold_OUTPUT/direct_P61609_Geobacter_sulfurreducens_PCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>p_value</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -508,6 +513,11 @@
       <c r="I2" t="n">
         <v>0.8884446221511395</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -546,6 +556,11 @@
       </c>
       <c r="I3" t="n">
         <v>0.8884446221511395</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Confirmed DR</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/30_Threshold_OUTPUT/direct_P61609_Geobacter_sulfurreducens_PCA.xlsx
+++ b/30_Threshold_OUTPUT/direct_P61609_Geobacter_sulfurreducens_PCA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,6 +474,11 @@
           <t>evaluation</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>correctness_%</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -518,6 +523,9 @@
           <t>Confirmed DR</t>
         </is>
       </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -561,6 +569,9 @@
         <is>
           <t>Confirmed DR</t>
         </is>
+      </c>
+      <c r="K3" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
